--- a/data/file_generation/input/data_57/2025-10-17_08_30_巴西甲_维多利亚[17]VS巴伊亚[6]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-17_08_30_巴西甲_维多利亚[17]VS巴伊亚[6]_标盘.xlsx
@@ -11869,26 +11869,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{663C70D6-698C-4F85-8E93-B306BAE19088}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38A5651B-CBB7-41C0-9111-D495AFAC1983}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62D36E9B-E169-4C58-9553-6BE30E7B4F88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D71906-F2CC-48DD-9E0A-CE50AD3554C2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96E6FCD-C70F-4D8C-A365-7D854BC66491}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F037EE5-D20B-48C3-A89C-8A0B77DCA1CF}"/>
 </file>